--- a/JsonConverter/ExcelFiles/Weapons.xlsx
+++ b/JsonConverter/ExcelFiles/Weapons.xlsx
@@ -21,37 +21,82 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <x:si>
+    <x:t>AttackRadius</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackDistance</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무검</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철검</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>돌검</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
+    <x:t>Tier</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>나무검</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돌검</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철검</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
+    <x:t>돌검이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무검이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무,돌</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무,철괴</x:t>
+  </x:si>
+  <x:si>
+    <x:t>철검이다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
   </x:si>
   <x:si>
     <x:t>Weapon_Iron_Sword</x:t>
@@ -60,55 +105,10 @@
     <x:t>Weapon_Stone_Sword</x:t>
   </x:si>
   <x:si>
+    <x:t>RequiredMaterial</x:t>
+  </x:si>
+  <x:si>
     <x:t>Weapon_Tree_Sword</x:t>
-  </x:si>
-  <x:si>
-    <x:t>돌검이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>철검이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무검이다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackCooldown</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDistance</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackRadius</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무,돌</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tier</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무,철괴</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Damage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredMaterial</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -119,7 +119,7 @@
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="8">
     <x:font>
       <x:name val="맑은 고딕"/>
       <x:sz val="10"/>
@@ -159,11 +159,6 @@
       <x:name val="&quot;맑은 고딕&quot;"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
-    </x:font>
-    <x:font>
-      <x:name val="돋움"/>
-      <x:sz val="11"/>
-      <x:color rgb="ff000000"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -857,7 +852,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="5"/>
@@ -866,60 +861,60 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="13.199999999999999">
       <x:c r="A2" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:16383" s="8" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="7" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
+      <x:c r="I3" s="7" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="F3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G3" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H3" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="P3" s="3"/>
       <x:c r="Q3" s="3"/>
@@ -928,16 +923,16 @@
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="9" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="4">
         <x:v>10</x:v>
@@ -952,7 +947,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I4" s="10" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="J4" s="10"/>
       <x:c r="K4" s="10"/>
@@ -963,13 +958,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
         <x:v>9</x:v>
@@ -987,7 +982,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I5" s="10" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J5" s="10"/>
       <x:c r="K5" s="10"/>
@@ -998,16 +993,16 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="4">
         <x:v>30</x:v>
@@ -1022,7 +1017,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I6" s="10" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="J6" s="10"/>
       <x:c r="K6" s="10"/>
@@ -2214,7 +2209,7 @@
     <x:row r="998" ht="15.75" customHeight="1"/>
     <x:row r="999" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69930553436279297" right="0.69930553436279297" top="0.75" bottom="0.75" header="0.51180553436279297" footer="0.51180553436279297"/>
+  <x:pageMargins left="0.69888889789581299" right="0.69888889789581299" top="0.75" bottom="0.75" header="0.51138889789581299" footer="0.51138889789581299"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </x:worksheet>
 </file>